--- a/database/seeders/data/pace-details.xlsx
+++ b/database/seeders/data/pace-details.xlsx
@@ -1,379 +1,379 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{DCEFD9AA-843B-B742-A9B3-F5D443316AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="135" windowWidth="20115" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="103">
   <si>
     <t>GRADE</t>
   </si>
   <si>
+    <t>PACE RANGE</t>
+  </si>
+  <si>
     <t>SUBJECTS</t>
   </si>
   <si>
     <t>RR</t>
   </si>
   <si>
+    <t>RR01 - RR12</t>
+  </si>
+  <si>
+    <t>ENGLISH</t>
+  </si>
+  <si>
+    <t>MATHS</t>
+  </si>
+  <si>
+    <t>SST</t>
+  </si>
+  <si>
+    <t>SCIENCE</t>
+  </si>
+  <si>
+    <t>WORD BUILDING</t>
+  </si>
+  <si>
     <t>GRADE 1</t>
   </si>
   <si>
-    <t>ENGLISH</t>
-  </si>
-  <si>
-    <t>MATHS</t>
+    <t>1001 - 1012</t>
   </si>
   <si>
     <t>ANIMAL SCIENCE</t>
   </si>
   <si>
-    <t>SST</t>
+    <t>BIBLE READING</t>
+  </si>
+  <si>
+    <t>GRADE 2</t>
+  </si>
+  <si>
+    <t>1013 - 1024</t>
+  </si>
+  <si>
+    <t>GRADE 3</t>
+  </si>
+  <si>
+    <t>1025 - 1036</t>
+  </si>
+  <si>
+    <t>LITERATURE</t>
+  </si>
+  <si>
+    <t>GRADE 4</t>
+  </si>
+  <si>
+    <t>1037 - 1048</t>
+  </si>
+  <si>
+    <t>GRADE 5</t>
+  </si>
+  <si>
+    <t>1049 - 1060</t>
+  </si>
+  <si>
+    <t>GRADE 6</t>
+  </si>
+  <si>
+    <t>1061 - 1072</t>
+  </si>
+  <si>
+    <t>GRADE 7</t>
+  </si>
+  <si>
+    <t>1073 - 1084</t>
+  </si>
+  <si>
+    <t>GRADE 8</t>
+  </si>
+  <si>
+    <t>1085 - 1096</t>
+  </si>
+  <si>
+    <t>AMERICAN HISTORY (SST 1)</t>
+  </si>
+  <si>
+    <t>LITERATURE 8</t>
+  </si>
+  <si>
+    <t>86 - 96 (ONLY EVEN NUMBERS)</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
+  </si>
+  <si>
+    <t>GRADE 9</t>
+  </si>
+  <si>
+    <t>1097 - 1108</t>
+  </si>
+  <si>
+    <t>ENGLISH 1</t>
+  </si>
+  <si>
+    <t>MATHS (ALGEBRA 1)</t>
+  </si>
+  <si>
+    <t>ETYMOLOGY</t>
+  </si>
+  <si>
+    <t>BIOLOGY (SCI)</t>
+  </si>
+  <si>
+    <t>WORLD GEOGRAPHY (SST)</t>
+  </si>
+  <si>
+    <t>1 - 10</t>
+  </si>
+  <si>
+    <t>APOLOGETICS</t>
+  </si>
+  <si>
+    <t>133-138</t>
+  </si>
+  <si>
+    <t>US CONSTITUTION</t>
+  </si>
+  <si>
+    <t>1 - 6</t>
+  </si>
+  <si>
+    <t>COLLEGE MATHS</t>
+  </si>
+  <si>
+    <t>133 - 138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLLECTIVISM </t>
+  </si>
+  <si>
+    <t>CIVICS</t>
+  </si>
+  <si>
+    <t>1133-1138</t>
+  </si>
+  <si>
+    <t>CIVICS AND ECONOMICS</t>
+  </si>
+  <si>
+    <t>CHRISTIAN GROWTH</t>
+  </si>
+  <si>
+    <t>CHRISTIAN COUNSELLING</t>
+  </si>
+  <si>
+    <t>1097 -1115</t>
+  </si>
+  <si>
+    <t>BUSINESS STUDIES</t>
+  </si>
+  <si>
+    <t>1133-1144</t>
+  </si>
+  <si>
+    <t>ADVANCED MATHS</t>
+  </si>
+  <si>
+    <t>TOURISM</t>
+  </si>
+  <si>
+    <t>1 - 20</t>
+  </si>
+  <si>
+    <t>HISTORY OF CIVILISATION (BHOC)</t>
+  </si>
+  <si>
+    <t>1133 -1144</t>
+  </si>
+  <si>
+    <t>ADVANCED BIOLOGY</t>
+  </si>
+  <si>
+    <t>1 -5</t>
+  </si>
+  <si>
+    <t>BRITISH LITERATURE</t>
+  </si>
+  <si>
+    <t>1 - 12</t>
+  </si>
+  <si>
+    <t>SUCCESSFUL LIVING</t>
+  </si>
+  <si>
+    <t>SPANISH</t>
+  </si>
+  <si>
+    <t>PERSONAL FINANCE</t>
+  </si>
+  <si>
+    <t>NUTRITION</t>
+  </si>
+  <si>
+    <t>HEALTH</t>
+  </si>
+  <si>
+    <t>97 - 108</t>
+  </si>
+  <si>
+    <t>FRENCH</t>
+  </si>
+  <si>
+    <t>FOUNDATION FOR LIVING</t>
+  </si>
+  <si>
+    <t>1085 - 1102</t>
+  </si>
+  <si>
+    <t>ECONOMICS &amp; MGT</t>
+  </si>
+  <si>
+    <t>1109 - 1115</t>
+  </si>
+  <si>
+    <t>AUTO MECHANICS</t>
+  </si>
+  <si>
+    <t>1 - 5</t>
+  </si>
+  <si>
+    <t>ASTRONOMY</t>
+  </si>
+  <si>
+    <t>ADVANCED ART</t>
+  </si>
+  <si>
+    <t>ELECTIVES</t>
+  </si>
+  <si>
+    <t>SST (AMERICAN HISTORY)</t>
+  </si>
+  <si>
+    <t>1133 - 1144</t>
+  </si>
+  <si>
+    <t>PHYSICS</t>
+  </si>
+  <si>
+    <t>1109-1115</t>
+  </si>
+  <si>
+    <t>BUSINESS STUDIES 2</t>
+  </si>
+  <si>
+    <t>1121 - 1132</t>
+  </si>
+  <si>
+    <t>CHEMISTRY</t>
+  </si>
+  <si>
+    <t>ENGLISH 3&amp;4</t>
+  </si>
+  <si>
+    <t>ALGEBRA 2</t>
+  </si>
+  <si>
+    <t>1121 - 1144</t>
+  </si>
+  <si>
+    <t>BIBLICAL STUDIES</t>
+  </si>
+  <si>
+    <t>GRADE 11</t>
   </si>
   <si>
     <t>ADVANCED</t>
   </si>
   <si>
-    <t>SCIENCE</t>
-  </si>
-  <si>
-    <t>WORD BUILDING</t>
-  </si>
-  <si>
-    <t>BIBLE READING</t>
-  </si>
-  <si>
-    <t>GRADE 2</t>
-  </si>
-  <si>
-    <t>GRADE 3</t>
-  </si>
-  <si>
-    <t>GRADE 4</t>
-  </si>
-  <si>
-    <t>GRADE 5</t>
-  </si>
-  <si>
-    <t>GRADE 6</t>
-  </si>
-  <si>
-    <t>GRADE 7</t>
-  </si>
-  <si>
-    <t>GRADE 8</t>
-  </si>
-  <si>
-    <t>GRADE 9</t>
-  </si>
-  <si>
-    <t>GENERAL</t>
+    <t>PHYSICAL SCIENCE 2</t>
+  </si>
+  <si>
+    <t>ENGLISH 2</t>
+  </si>
+  <si>
+    <t>GEOMETRY (MATH)</t>
+  </si>
+  <si>
+    <t>1109 - 1120</t>
+  </si>
+  <si>
+    <t>GRADE 10</t>
   </si>
   <si>
     <t>INTERMIDIATE</t>
   </si>
   <si>
-    <t>GRADE 10</t>
-  </si>
-  <si>
-    <t>GRADE 11</t>
-  </si>
-  <si>
-    <t>ECONOMICS &amp; MGT</t>
+    <t>98 - 108 (ONLY EVEN NUMBERS)</t>
+  </si>
+  <si>
+    <t>ACE LITERATURE 9</t>
   </si>
   <si>
     <t>PHYSICAL SCIENCE 1</t>
-  </si>
-  <si>
-    <t>AMERICAN HISTORY (SST 1)</t>
-  </si>
-  <si>
-    <t>LITERATURE 8</t>
-  </si>
-  <si>
-    <t>ENGLISH 1</t>
-  </si>
-  <si>
-    <t>BIOLOGY (SCI)</t>
-  </si>
-  <si>
-    <t>ETYMOLOGY</t>
-  </si>
-  <si>
-    <t>ACE LITERATURE 9</t>
-  </si>
-  <si>
-    <t>MATHS (ALGEBRA 1)</t>
-  </si>
-  <si>
-    <t>BIBLICAL STUDIES</t>
-  </si>
-  <si>
-    <t>GEOMETRY (MATH)</t>
-  </si>
-  <si>
-    <t>ENGLISH 2</t>
-  </si>
-  <si>
-    <t>PHYSICAL SCIENCE 2</t>
-  </si>
-  <si>
-    <t>ALGEBRA 2</t>
-  </si>
-  <si>
-    <t>ENGLISH 3&amp;4</t>
-  </si>
-  <si>
-    <t>ADVANCED BIOLOGY</t>
-  </si>
-  <si>
-    <t>CHEMISTRY</t>
-  </si>
-  <si>
-    <t>BUSINESS STUDIES 2</t>
-  </si>
-  <si>
-    <t>PHYSICS</t>
-  </si>
-  <si>
-    <t>SST (AMERICAN HISTORY)</t>
-  </si>
-  <si>
-    <t>ELECTIVES</t>
-  </si>
-  <si>
-    <t>ADVANCED ART</t>
-  </si>
-  <si>
-    <t>AUTO MECHANICS</t>
-  </si>
-  <si>
-    <t>FOUNDATION FOR LIVING</t>
-  </si>
-  <si>
-    <t>FRENCH</t>
-  </si>
-  <si>
-    <t>HEALTH</t>
-  </si>
-  <si>
-    <t>NUTRITION</t>
-  </si>
-  <si>
-    <t>PERSONAL FINANCE</t>
-  </si>
-  <si>
-    <t>SPANISH</t>
-  </si>
-  <si>
-    <t>SUCCESSFUL LIVING</t>
-  </si>
-  <si>
-    <t>BRITISH LITERATURE</t>
-  </si>
-  <si>
-    <t>TOURISM</t>
-  </si>
-  <si>
-    <t>ADVANCED MATHS</t>
-  </si>
-  <si>
-    <t>BUSINESS STUDIES</t>
-  </si>
-  <si>
-    <t>CHRISTIAN COUNSELLING</t>
-  </si>
-  <si>
-    <t>CHRISTIAN GROWTH</t>
-  </si>
-  <si>
-    <t>CIVICS AND ECONOMICS</t>
-  </si>
-  <si>
-    <t>CIVICS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COLLECTIVISM </t>
-  </si>
-  <si>
-    <t>COLLEGE MATHS</t>
-  </si>
-  <si>
-    <t>US CONSTITUTION</t>
-  </si>
-  <si>
-    <t>APOLOGETICS</t>
-  </si>
-  <si>
-    <t>LITERATURE</t>
-  </si>
-  <si>
-    <t>PACE RANGE</t>
-  </si>
-  <si>
-    <t>1001 - 1012</t>
-  </si>
-  <si>
-    <t>RR01 - RR12</t>
-  </si>
-  <si>
-    <t>1013 - 1024</t>
-  </si>
-  <si>
-    <t>1025 - 1036</t>
-  </si>
-  <si>
-    <t>1037 - 1048</t>
-  </si>
-  <si>
-    <t>1049 - 1060</t>
-  </si>
-  <si>
-    <t>1061 - 1072</t>
-  </si>
-  <si>
-    <t>1073 - 1084</t>
-  </si>
-  <si>
-    <t>1085 - 1096</t>
-  </si>
-  <si>
-    <t>1097 - 1108</t>
-  </si>
-  <si>
-    <t>1109 - 1120</t>
-  </si>
-  <si>
-    <t>1121 - 1144</t>
-  </si>
-  <si>
-    <t>WORLD GEOGRAPHY (SST)</t>
-  </si>
-  <si>
-    <t>98 - 108 (ONLY EVEN NUMBERS)</t>
-  </si>
-  <si>
-    <t>86 - 96 (ONLY EVEN NUMBERS)</t>
-  </si>
-  <si>
-    <t>1121 - 1132</t>
-  </si>
-  <si>
-    <t>1133 - 1144</t>
-  </si>
-  <si>
-    <t>97 - 108</t>
-  </si>
-  <si>
-    <t>ASTRONOMY</t>
-  </si>
-  <si>
-    <t>1 - 5</t>
-  </si>
-  <si>
-    <t>1 - 10</t>
-  </si>
-  <si>
-    <t>1 - 6</t>
-  </si>
-  <si>
-    <t>1 - 12</t>
-  </si>
-  <si>
-    <t>1 -5</t>
-  </si>
-  <si>
-    <t>1133 -1144</t>
-  </si>
-  <si>
-    <t>1 - 20</t>
-  </si>
-  <si>
-    <t>HISTORY OF CIVILISATION (BHOC)</t>
-  </si>
-  <si>
-    <t>1097 -1115</t>
-  </si>
-  <si>
-    <t>133 - 138</t>
-  </si>
-  <si>
-    <t>1085 - 1102</t>
-  </si>
-  <si>
-    <t>1109-1115</t>
-  </si>
-  <si>
-    <t>1133-1144</t>
-  </si>
-  <si>
-    <t>1133-1138</t>
-  </si>
-  <si>
-    <t>133-138</t>
-  </si>
-  <si>
-    <t>1109 - 1115</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -395,26 +395,26 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -422,17 +422,17 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
@@ -442,7 +442,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
@@ -450,49 +450,49 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -500,10 +500,10 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -512,82 +512,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="3" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="4" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="5" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="6" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="7" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="8" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="9" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
@@ -699,7 +691,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -872,53 +864,56 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D122"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:D123"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12.375" customWidth="1"/>
-    <col min="2" max="2" width="20.17578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.8046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.0546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20.17578125" customWidth="true" style="0"/>
+    <col min="3" max="3" width="30.8046875" customWidth="true" style="0"/>
+    <col min="4" max="4" width="29.0546875" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" customHeight="1" ht="23.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" s="6"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1" t="s">
@@ -926,59 +921,59 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="6"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="8"/>
       <c r="B7" s="9"/>
       <c r="C7" s="10"/>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="1" t="s">
@@ -986,59 +981,59 @@
       </c>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
       <c r="D15" s="11"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" s="1"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
       <c r="C18" s="1" t="s">
@@ -1046,67 +1041,67 @@
       </c>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
       <c r="C19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
       <c r="C20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
       <c r="C21" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="10"/>
       <c r="D22" s="11"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
       <c r="C25" s="1" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
       <c r="C26" s="1" t="s">
@@ -1114,67 +1109,67 @@
       </c>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
       <c r="C27" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
       <c r="C29" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="10"/>
       <c r="D30" s="11"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32" s="1"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D33" s="1"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="1" t="s">
@@ -1182,67 +1177,67 @@
       </c>
       <c r="D34" s="1"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
       <c r="C35" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
       <c r="C37" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D37" s="1"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="10"/>
       <c r="D38" s="11"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D40" s="1"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
       <c r="C41" s="1" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D41" s="1"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
       <c r="C42" s="1" t="s">
@@ -1250,67 +1245,67 @@
       </c>
       <c r="D42" s="1"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" s="6"/>
       <c r="B43" s="7"/>
       <c r="C43" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" s="6"/>
       <c r="B44" s="7"/>
       <c r="C44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" s="1"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" s="6"/>
       <c r="B45" s="7"/>
       <c r="C45" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D45" s="1"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="10"/>
       <c r="D46" s="11"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
       <c r="C48" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D48" s="1"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" s="6"/>
       <c r="B49" s="7"/>
       <c r="C49" s="1" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D49" s="1"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" s="6"/>
       <c r="B50" s="7"/>
       <c r="C50" s="1" t="s">
@@ -1318,67 +1313,67 @@
       </c>
       <c r="D50" s="1"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" s="6"/>
       <c r="B51" s="7"/>
       <c r="C51" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" s="6"/>
       <c r="B52" s="7"/>
       <c r="C52" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D52" s="1"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" s="6"/>
       <c r="B53" s="7"/>
       <c r="C53" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D53" s="1"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" s="8"/>
       <c r="B54" s="9"/>
       <c r="C54" s="10"/>
       <c r="D54" s="11"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="4"/>
       <c r="B56" s="5"/>
       <c r="C56" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" s="6"/>
       <c r="B57" s="7"/>
       <c r="C57" s="1" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D57" s="1"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" s="6"/>
       <c r="B58" s="7"/>
       <c r="C58" s="1" t="s">
@@ -1386,145 +1381,143 @@
       </c>
       <c r="D58" s="1"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" s="6"/>
       <c r="B59" s="7"/>
       <c r="C59" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" s="6"/>
       <c r="B60" s="7"/>
       <c r="C60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D60" s="1"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
       <c r="C61" s="10"/>
       <c r="D61" s="11"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="4"/>
       <c r="B63" s="5"/>
       <c r="C63" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D63" s="1"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" s="6"/>
       <c r="B64" s="7"/>
       <c r="C64" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" s="6"/>
       <c r="B65" s="7"/>
       <c r="C65" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D65" s="1"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" s="6"/>
       <c r="B66" s="7"/>
       <c r="C66" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D66" s="1"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" s="6"/>
       <c r="B67" s="7"/>
       <c r="C67" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D67" s="1"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" s="6"/>
       <c r="B68" s="7"/>
       <c r="C68" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="6"/>
       <c r="B69" s="7"/>
-      <c r="C69" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="C69" s="1"/>
       <c r="D69" s="1"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" s="8"/>
       <c r="B70" s="9"/>
       <c r="C70" s="10"/>
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="1:4" ht="21" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" customHeight="1" ht="21">
       <c r="A71" s="18" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
       <c r="C73" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D73" s="1"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" s="6"/>
       <c r="B74" s="7"/>
       <c r="C74" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D74" s="1"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" s="6"/>
       <c r="B75" s="7"/>
       <c r="C75" s="1" t="s">
@@ -1532,457 +1525,467 @@
       </c>
       <c r="D75" s="1"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" s="6"/>
       <c r="B76" s="7"/>
       <c r="C76" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D76" s="1"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" s="6"/>
       <c r="B77" s="7"/>
       <c r="C77" s="1" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="D77" s="1"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" s="6"/>
       <c r="B78" s="7"/>
       <c r="C78" s="1" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="6"/>
       <c r="B79" s="7"/>
       <c r="C79" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D79" s="1"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="8"/>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="11"/>
-    </row>
-    <row r="81" spans="1:4" ht="21" x14ac:dyDescent="0.3">
-      <c r="A81" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="20"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="5"/>
+        <v>101</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="6"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D80" s="1"/>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="8"/>
+      <c r="B81" s="9"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="11"/>
+    </row>
+    <row r="82" spans="1:4" customHeight="1" ht="21">
+      <c r="A82" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="20"/>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="C83" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="6"/>
-      <c r="B84" s="7"/>
+        <v>91</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="4"/>
+      <c r="B84" s="5"/>
       <c r="C84" s="1" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" s="6"/>
       <c r="B85" s="7"/>
       <c r="C85" s="1" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="8"/>
-      <c r="B86" s="9"/>
-      <c r="C86" s="10"/>
-      <c r="D86" s="11"/>
-    </row>
-    <row r="87" spans="1:4" ht="23.25" x14ac:dyDescent="0.3">
-      <c r="A87" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="14"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
+    <row r="86" spans="1:4">
+      <c r="A86" s="6"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="8"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="10"/>
+      <c r="D87" s="11"/>
+    </row>
+    <row r="88" spans="1:4" customHeight="1" ht="23.25">
+      <c r="A88" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B88" s="13"/>
+      <c r="C88" s="13"/>
+      <c r="D88" s="14"/>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C89" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D89" s="1"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="6"/>
-      <c r="B90" s="7"/>
+        <v>91</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="4"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91" s="6"/>
       <c r="B91" s="7"/>
       <c r="C91" s="1" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92" s="6"/>
       <c r="B92" s="7"/>
       <c r="C92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" s="6"/>
       <c r="B93" s="7"/>
       <c r="C93" s="1" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" s="6"/>
       <c r="B94" s="7"/>
       <c r="C94" s="1" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95" s="6"/>
       <c r="B95" s="7"/>
       <c r="C95" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D95" s="1"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="8"/>
-      <c r="B96" s="9"/>
-      <c r="C96" s="10"/>
-      <c r="D96" s="11"/>
-    </row>
-    <row r="97" spans="1:4" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
-      <c r="D97" s="17"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="1"/>
-      <c r="C98" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="6"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D96" s="1"/>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="8"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="11"/>
+    </row>
+    <row r="98" spans="1:4" customHeight="1" ht="25.5">
+      <c r="A98" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B98" s="16"/>
+      <c r="C98" s="16"/>
+      <c r="D98" s="17"/>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
       <c r="C99" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>88</v>
+        <v>43</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A89:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:D97"/>
+  <mergeCells>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A90:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:D98"/>
     <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A73:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A83:B86"/>
-    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="A73:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A84:B87"/>
+    <mergeCell ref="C87:D87"/>
     <mergeCell ref="A48:B54"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="A56:B61"/>
@@ -2002,7 +2005,8 @@
     <mergeCell ref="A17:B22"/>
     <mergeCell ref="C22:D22"/>
   </mergeCells>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
 </worksheet>
 </file>